--- a/HLJT_online_PsychoPy/hljt_files/Instructions_left_hand.xlsx
+++ b/HLJT_online_PsychoPy/hljt_files/Instructions_left_hand.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github_repos/HLJT/HLJT_local/hljt_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/HLJT/HLJT_local_PsychoPy/hljt_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{B6C2750F-7572-42CC-AC1E-BD073640EEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F31C648-6E1A-4663-B91D-ECA52F9ADDD2}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{B6C2750F-7572-42CC-AC1E-BD073640EEDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{645C3403-BE59-4279-A766-EFF7996636FE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3128DB0A-6163-4D40-98DA-1667AB584357}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{3128DB0A-6163-4D40-98DA-1667AB584357}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -279,13 +279,6 @@
     <t>inst_msg_DE</t>
   </si>
   <si>
-    <t>Anweisungen:
-In dieser Aufgabe sehen Sie Bilder von linken oder rechten Händen, deren Handflächen nach oben oder unten zeigen. Die Bilder werden in verschiedenen Winkeln gedreht.
-Ihre Aufgabe ist es zu bestimmen, ob das Bild einer linken oder rechten Hand entspricht.
-Ihr Ziel ist es, sowohl SCHNELL als auch GENAU zu antworten.
-Jedes Bild wird angezeigt, bis Sie geantwortet haben. Das nächste Bild erscheint automatisch.</t>
-  </si>
-  <si>
     <t>Bitte verwenden Sie nur Ihren ZEIGEFINGER und MITTELFINGER der LINKEN HAND, um zu antworten.
 Legen Sie Ihren Zeigefinger auf die Taste „H“ und den Mittelfinger auf die Taste „G“ Ihrer Tastatur.
 Zum Antworten:
@@ -294,10 +287,68 @@
 Halten Sie Ihre andere Hand auf dem Tisch, in derselben Position und so ruhig wie möglich.</t>
   </si>
   <si>
-    <t>Nach jedem Bild erhalten Sie ein kurzes Feedback zu Ihrer Antwort:
-Wenn Sie korrekt antworten, wird das entsprechende Feld grün.
-Wenn Sie falsch antworten, wird das entsprechende Feld rot.
-Denken Sie daran, dass Ihr Ziel darin besteht, so genau und schnell wie möglich zu antworten.</t>
+    <t>Instruktionen:
+In dieser Aufgabe sehen Sie Bilder von linken oder rechten Händen, deren Handfläche nach oben oder unten zeigt. Die Bilder werden in verschiedenen Winkeln gedreht.
+Ihre Aufgabe ist es zu bestimmen, ob das Bild einer linken oder rechten Hand entspricht.
+Ihr Ziel ist es, so schnell UND korrekt wie möglich zu antworten.
+Jedes Bild wird angezeigt, bis Sie geantwortet haben. Das nächste Bild erscheint automatisch.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nach jedem Bild erhalten Sie ein kurzes Feedback zu Ihrer Antwort:
+Wenn Sie korrekt antworten, wird das entsprechende Feld </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>grün</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+Wenn Sie falsch antworten, wird das entsprechende Feld </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Erinnern Sie sich an Ihr Ziel so schnell und korrekt wie möglich zu antworten.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -374,12 +425,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -395,10 +449,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -745,8 +795,8 @@
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="F2">
         <v>0.6</v>
@@ -769,7 +819,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>0.6</v>
